--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>290</v>
+        <v>364</v>
       </c>
       <c r="D3">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>426</v>
